--- a/data/trans_orig/IP07A13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A13-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40986</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58223</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42865</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60688</t>
+          <t>60963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87418</t>
+          <t>87387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113417</t>
+          <t>112849</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59264</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76376</t>
+          <t>76617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68635</t>
+          <t>68037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86645</t>
+          <t>86759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132863</t>
+          <t>133665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158440</t>
+          <t>158873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27558</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65102</t>
+          <t>64436</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87534</t>
+          <t>86681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66105</t>
+          <t>66014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88498</t>
+          <t>87703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137398</t>
+          <t>137852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167334</t>
+          <t>168391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>78835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>101496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92390</t>
+          <t>92166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114457</t>
+          <t>114999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176870</t>
+          <t>177375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208533</t>
+          <t>210563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30735</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>38144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59527</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111098</t>
+          <t>112011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139940</t>
+          <t>140390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115134</t>
+          <t>114200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142308</t>
+          <t>142672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233703</t>
+          <t>235384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273662</t>
+          <t>275696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141788</t>
+          <t>143450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171510</t>
+          <t>172180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166959</t>
+          <t>167474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194767</t>
+          <t>197175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>317405</t>
+          <t>319018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361235</t>
+          <t>359750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44791</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>56956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>80337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 96,87%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2012 (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47569</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67969</t>
+          <t>68096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71750</t>
+          <t>70776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104236</t>
+          <t>104669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132196</t>
+          <t>133205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>73740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94717</t>
+          <t>95037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70669</t>
+          <t>69906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91206</t>
+          <t>90858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151861</t>
+          <t>150885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179404</t>
+          <t>179950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,58%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28643</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37174</t>
+          <t>37272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56609</t>
+          <t>55951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60029</t>
+          <t>58337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78981</t>
+          <t>78784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100943</t>
+          <t>102568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130483</t>
+          <t>129648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88796</t>
+          <t>88985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110443</t>
+          <t>109375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68061</t>
+          <t>67399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88837</t>
+          <t>88309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162786</t>
+          <t>162737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191805</t>
+          <t>192579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>30631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47291</t>
+          <t>46788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90558</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117215</t>
+          <t>116629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116048</t>
+          <t>115467</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143773</t>
+          <t>144513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214992</t>
+          <t>214694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254501</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169633</t>
+          <t>169586</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198426</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144107</t>
+          <t>145291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171993</t>
+          <t>174990</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321210</t>
+          <t>322979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363247</t>
+          <t>364575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42677</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70958</t>
+          <t>70073</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89305</t>
+          <t>90259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113340</t>
+          <t>111885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95733</t>
+          <t>95750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118578</t>
+          <t>117463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193033</t>
+          <t>190549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223659</t>
+          <t>222602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65479</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>87551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56197</t>
+          <t>55885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78378</t>
+          <t>77511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129656</t>
+          <t>129973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160398</t>
+          <t>161607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60925</t>
+          <t>62300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83139</t>
+          <t>82777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75891</t>
+          <t>76395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97890</t>
+          <t>99155</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144238</t>
+          <t>143420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175502</t>
+          <t>175790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66810</t>
+          <t>67821</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88419</t>
+          <t>89040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60929</t>
+          <t>59693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82613</t>
+          <t>81842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133821</t>
+          <t>133448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164407</t>
+          <t>165717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>22121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40533</t>
+          <t>39958</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157027</t>
+          <t>157612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190398</t>
+          <t>187861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176908</t>
+          <t>179298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208856</t>
+          <t>209545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344438</t>
+          <t>342511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390059</t>
+          <t>390229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171255</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>123327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154751</t>
+          <t>153934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270164</t>
+          <t>272051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313949</t>
+          <t>315585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A13-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51197</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42972</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61194</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>49238</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41262</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>58909</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>40627</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>58163</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51197</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>42451</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60963</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87387</t>
+          <t>89173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112849</t>
+          <t>113845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77701</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66928</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>85673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,54%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>67871</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58427</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>76617</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59325</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>77403</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>53,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>77701</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>68037</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86759</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>54,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>132923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158873</t>
+          <t>158081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -948,64 +948,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10486</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6502</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16316</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9065</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5228</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14672</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5428</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15029</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,18%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10486</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16411</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>4,3%</t>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>27188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1496</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4685</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5231</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5705</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4439</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>635</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3180</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3621</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126174</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126174</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>76888</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65130</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87353</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>75962</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64436</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>86681</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>66448</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>87364</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>76888</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>66014</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>87703</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137852</t>
+          <t>137171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168391</t>
+          <t>167986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>103325</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>92056</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>115243</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89871</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78835</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>101496</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79192</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>99538</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>46,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>103325</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>92166</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>114999</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177375</t>
+          <t>177078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210563</t>
+          <t>208562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,58%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23140</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16545</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30913</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25495</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18295</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18488</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33279</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>13,24%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23140</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16965</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30820</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59202</t>
+          <t>59307</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -1748,102 +1748,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3614</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3589</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3170</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1352</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4575</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4099</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4676</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2911</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192621</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192621</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192621</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>128085</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>113629</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>141825</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>125200</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>112011</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>140390</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>112828</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>140096</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>39,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>128085</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>114200</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>142672</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235384</t>
+          <t>233572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>275696</t>
+          <t>274572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>181026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>167439</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>197448</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>157742</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>143450</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>172180</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>142912</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>171787</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>49,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>54,01%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>181026</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>167474</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>197175</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319018</t>
+          <t>319367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359750</t>
+          <t>359381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33626</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25449</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44275</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,73%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>34560</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>25316</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>43078</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>26775</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>44395</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33626</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>25175</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>43263</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56956</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80337</t>
+          <t>82307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5934</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3679</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2933</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2216</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5859</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2543,87 +2543,87 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2966</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>473</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>318795</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>318795</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>318795</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2012 (tasa de respuesta: 96,87%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60816</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>51120</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71354</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>57156</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47792</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>68096</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>47385</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>67644</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60816</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51297</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>70776</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104669</t>
+          <t>105134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133205</t>
+          <t>134190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70194</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>90811</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>84450</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>73740</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>95037</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>73956</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>94266</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>55,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>48,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>81164</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69906</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>90858</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150885</t>
+          <t>151622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179950</t>
+          <t>180143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11354</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17373</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15315</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5215</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15262</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,31%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11354</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6605</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17741</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -3337,92 +3337,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5512</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5482</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3450,107 +3450,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3473</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3981</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156049</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156049</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156049</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151141</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151141</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151141</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156049</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156049</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156049</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>68477</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58138</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78210</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46663</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37272</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55951</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37909</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57746</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>68477</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>58337</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>78784</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,4%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102568</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129648</t>
+          <t>128848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78491</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68344</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>89010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>99419</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>88985</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>109375</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>88070</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>109550</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>60,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78491</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67399</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>88309</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162737</t>
+          <t>161660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192579</t>
+          <t>192348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22221</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15595</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29362</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14596</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9538</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21756</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8951</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21335</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,84%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>22221</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16312</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30631</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27523</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>48284</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3961</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8470</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2720</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6849</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6179</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8273</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -4132,74 +4132,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2574</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1741</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5805</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3667</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173784</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173784</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173784</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165139</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165139</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165139</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173784</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173784</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173784</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>129293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>115443</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144200</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>103819</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>88851</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>116629</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>90670</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>117660</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,82%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>129293</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>115467</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,2%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214694</t>
+          <t>215100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253258</t>
+          <t>253866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>159655</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>145424</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>174701</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>183869</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>169586</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>198595</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>168599</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>197982</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>58,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>62,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>159655</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>145291</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>174990</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>48,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>322979</t>
+          <t>321600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364575</t>
+          <t>361609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33575</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25052</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>42934</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>24132</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17422</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32626</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17801</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>33519</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,63%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33575</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>25122</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>42840</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46228</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70073</t>
+          <t>70390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2687</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10853</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2720</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6161</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2688</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4819,67 +4819,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4622</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1741</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5403</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4686</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>329833</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>329833</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>329833</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>449</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>316280</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>316280</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>316280</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>329833</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>329833</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>329833</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>106471</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>96139</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>118328</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>101299</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>90259</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>111885</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>90115</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>112010</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>106471</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>95750</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>117463</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190549</t>
+          <t>191954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>222602</t>
+          <t>222765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67249</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56027</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77385</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77061</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66611</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87551</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>66670</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87774</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>41,43%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67249</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55885</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77511</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129973</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161607</t>
+          <t>159426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8982</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15820</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6977</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3458</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12071</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12288</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8982</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15313</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -5613,107 +5613,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1397</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4955</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>184099</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>184099</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>184099</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>184099</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>184099</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>184099</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87134</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76868</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99184</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>72362</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62300</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>82777</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61074</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>82702</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>42,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87134</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>76395</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>99155</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,06%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143420</t>
+          <t>145301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175790</t>
+          <t>176113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71147</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60180</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81738</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77964</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67821</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89040</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67323</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89247</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>45,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71147</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>59693</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81842</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133448</t>
+          <t>134047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165717</t>
+          <t>165464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15180</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10151</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22929</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15514</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22121</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22330</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,12%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15180</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9333</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>22338</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22915</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39958</t>
+          <t>39771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3294</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7590</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7724</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -6413,102 +6413,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4880</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5018</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1580</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170127</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170127</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170127</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>193604</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>176521</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>208835</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>173661</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>157612</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>187861</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>158335</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>190086</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>48,77%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>193604</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>179298</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>209545</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342511</t>
+          <t>346473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390229</t>
+          <t>389391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>138395</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122961</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>154049</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>155025</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>140888</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>139404</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>169624</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>138395</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123327</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>153934</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272051</t>
+          <t>270380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315585</t>
+          <t>312733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -6869,67 +6869,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>24162</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17269</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33570</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>22491</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>15796</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>30961</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>30904</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,32%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>24162</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>17189</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>32664</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59550</t>
+          <t>58556</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4647</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3294</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7455</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6715</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5167</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1638</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6238</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2969</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>358146</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>358146</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>358146</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356110</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356110</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356110</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>358146</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>358146</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>358146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
